--- a/03_pagos/yape/motor_matching/trazabilidad/trazabilidad_2026_05.xlsx
+++ b/03_pagos/yape/motor_matching/trazabilidad/trazabilidad_2026_05.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sin_identificar" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Ambiguos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Pagos_multiples" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Maestro_inexacto" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +31,91 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="005B21B6"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00185FA5"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00085041"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007C3003"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="005B21B6"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="005B21B6"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00185FA5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00065F46"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00185FA5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00085041"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00085041"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="007C3003"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00854F0B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00854F0B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00A32D2D"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -43,11 +124,56 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A235A"/>
+        <fgColor rgb="00F4ECF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1F5EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FFF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAEEDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBF0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -69,14 +195,112 @@
         <color rgb="00FFFFFF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,126 +667,1263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="1" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="1" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="1" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>¿QUIÉN ES?</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr"/>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>¿QUÉ HIZO EL BANCO?</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr"/>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>¿CÓMO SE RESOLVIÓ?</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr"/>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>¿CUÁNDO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>USER_ID</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>NOMBRE</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
           <t>ORIGEN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>DESTINO</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>MONTO</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>MENSAJE</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>LOTE</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PLIN - DEYSI STEFANY VENTURO ROSALES</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>MOTIVO</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>CICLO</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>FECHA_CORRECCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>U0011</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>ISABEL PUNTILLO VEGA</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - GRICEL DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr"/>
+      <c r="G3" s="13" t="inlineStr"/>
+      <c r="H3" s="14" t="inlineStr"/>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>03/05/2026 05:45:29</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr"/>
+      <c r="N3" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>U0102</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>MARIA GODO SIFUENTES</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - ELIAS AGAPITO SALES BLAS</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr"/>
+      <c r="G4" s="13" t="inlineStr"/>
+      <c r="H4" s="14" t="inlineStr"/>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 19:54:37</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="inlineStr"/>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>U0136</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>NELSON COSME GARCILAZO</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>NELSON COS*</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr"/>
+      <c r="H5" s="14" t="inlineStr"/>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 19:02:55</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr"/>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>U0101</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>MERCADO TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>RIMENITA MUN*</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr"/>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="14" t="inlineStr"/>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 18:39:22</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M6" s="16" t="inlineStr"/>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>MZ-19 no existe en planilla</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>U0075</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>HERMELINDA JARA TRUJILLO</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>CRISTOPHER GON*</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 18:27:59</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>14/05/2026 19:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NELLY DE-*</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>U0233</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>LEONCIO CASTILLEJO CAPCHA</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>MATILDE BLA*</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 14:56:37</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="inlineStr"/>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>U0171</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>JULIA CARDENAS ALVARADO</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>EDWIN PAC*</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 13:54:17</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>14/05/2026 19:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PLIN - YASNINA NELLY JAIMES TRUJILLO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr"/>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="10" t="inlineStr"/>
+      <c r="B10" s="11" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>JULIANA MED*</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 13:31:48</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>BLANCO</t>
+        </is>
+      </c>
+      <c r="L10" s="15" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr"/>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>U0170</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>ROSA CARDENAS ALVARADO</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>VILMA ROS*</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 13:29:40</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>U0184</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>MARCELO CHINCHAY REGALADO</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>MARCELO CHI*</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 11:22:08</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="inlineStr"/>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>U0172</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>OTILIA RAMIRES LUCIANO</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>ELMER LUN*</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 08:00:03</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L13" s="15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>14/05/2026 19:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PAUL TRU*</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="M13" s="16" t="inlineStr"/>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>U0413</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>ELENA JUANA CASTILLEJO CAPCHA</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>YONEL SAL*</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr"/>
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr"/>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 07:22:05</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="inlineStr"/>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>U0105</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>TOLENTINO JULCA MORENO</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>ELMA ROM*</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 07:11:43</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>14/05/2026 19:16</t>
+      <c r="M15" s="16" t="inlineStr"/>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>U0224</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>SANTOS LUNA FLORES</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>NAISA LUN*</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr"/>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>01/05/2026 18:11:05</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" s="16" t="inlineStr"/>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>U0466</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>MARIA SEGURA MELCHOR</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>EDWIN CAR*</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>01/05/2026 17:52:26</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="inlineStr"/>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>E1-14 no existe en planilla</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>U0086</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>FELIPE DOMINGO VENTURO CAPCHA</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>BCP - VENTURO CAPCHA FELIPE DOMINGO</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr"/>
+      <c r="H18" s="14" t="inlineStr"/>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>01/05/2026 12:57:33</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M18" s="16" t="inlineStr"/>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>U0409</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>WILSON PATRICIO HUAYTA</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - WILSON PATRICIO</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr"/>
+      <c r="G19" s="13" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr"/>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>01/05/2026 12:40:36</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="L19" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>U0112</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>JANETH CHAVEZ CASTILLEJO</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>BCP - CADILLO VENTURO DINA NICETA</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr"/>
+      <c r="G20" s="13" t="inlineStr"/>
+      <c r="H20" s="14" t="inlineStr"/>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>01/05/2026 12:26:54</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M20" s="16" t="inlineStr"/>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>U0310</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>ROSA TOLENTINO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>ROSA TOL*</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr"/>
+      <c r="G21" s="13" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>29/04/2026 19:57:27</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="inlineStr"/>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>U0009</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>JHONI MELGAREJO BEDON</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - BLANCA LUZ RAFAELE OCHOA</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr"/>
+      <c r="G22" s="13" t="inlineStr"/>
+      <c r="H22" s="14" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>29/04/2026 11:14:30</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L22" s="15" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
+      <c r="M22" s="16" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>sin mensaje ni maestro</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -573,38 +1934,524 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="1" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="1" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="1" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="1" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>¿QUIÉN ES?</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr"/>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>¿QUÉ HIZO EL BANCO?</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr"/>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
+          <t>CANDIDATOS</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr"/>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>ELEGIDO</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr"/>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>¿CUÁNDO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>USER_ID</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>NOMBRE</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
           <t>ORIGEN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MZ</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LOTE</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>MONTO</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>MENSAJE</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="20" t="inlineStr">
+        <is>
+          <t>CANDIDATOS</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>MZ_FINAL</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>LOTE_FINAL</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>CICLO</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>FECHA_CORRECCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>U0070</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>JUAN VENTURO CAPCHA</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - Deysi Stefany Venturo Rosales</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 23:08:41</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>D-1(38,-23) · D-19(47,-32)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>U0070</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>JUAN VENTURO CAPCHA</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - Deysi Stefany Venturo Rosales</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 23:02:47</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>D-1(38,0) · D-19(47,-9)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>U0168</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>AURELIO DE LA CRUZ PEREZ</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Nelly De-*</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>pago de consumo de agua de 2 meses    Aurelio De la</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 10:25:11</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>I-6(40,0) · O-15(22,+18)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>U0202</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>MARINO FEDERICO JAIMES VIDAL</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - YASNINA NELLY JAIMES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>01/05/2026 15:18:07</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>K-10(10,0) · E1-3(12,-2) · W-7(8,+2)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>U0465</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>KAREN JAIMES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - YASNINA NELLY JAIMES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>01/05/2026 15:17:04</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>E1-3(12,0) · K-10(10,+2) · W-7(8,+4)</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>U0202</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>MARINO FEDERICO JAIMES VIDAL</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - YASNINA NELLY JAIMES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>01/05/2026 15:16:04</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>K-10(10,0) · E1-3(12,-2) · W-7(8,+2)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>U0374</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>YASMINA JAIMES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>PLIN - YASNINA NELLY JAIMES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>01/05/2026 15:14:59</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>W-7(8,0) · K-10(10,-2) · E1-3(12,-4)</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -615,169 +2462,832 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="1" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="1" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="1" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>¿QUIÉN ES?</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr"/>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>¿QUÉ HIZO EL BANCO?</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr"/>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>ASIGNACIÓN POR LOTE</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr"/>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>¿CUÁNDO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>USER_ID</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>NOMBRE</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
           <t>ORIGEN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>MONTO_TOTAL</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>MENSAJE</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>MZ</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>LOTE</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>DEUDA</t>
+        </is>
+      </c>
+      <c r="L2" s="22" t="inlineStr">
         <is>
           <t>MONTO_ASIGNADO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>DIFF</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>CICLO</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>FECHA_CORRECCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>U0092</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>GREGORIO TRUJILLO LEON</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>WILLIAM TRU*|02/05/2026 09:02:49</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="F3" s="14" t="inlineStr"/>
+      <c r="G3" s="12" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K3" s="23" t="inlineStr"/>
+      <c r="L3" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="M3" s="23" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>U0287</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>JULIA ROSALES CULLA</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>WILLIAM TRU*|02/05/2026 09:02:49</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr"/>
+      <c r="G4" s="12" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>11A</t>
+        </is>
+      </c>
+      <c r="K4" s="23" t="inlineStr"/>
+      <c r="L4" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="23" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>U0239</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>ROGELIO ROSALES CUYA</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>WILLIAM TRU*|02/05/2026 09:02:49</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="12" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr"/>
+      <c r="L5" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" s="23" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>U0196</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>YULY LISBETH TRUJILLO CRUZ</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>PAUL TRU*|02/05/2026 08:58:08</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="F6" s="14" t="inlineStr"/>
+      <c r="G6" s="12" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr"/>
+      <c r="L6" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" s="23" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>U0197</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>EMILIA CRUZ OLORTEGUI</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>PAUL TRU*|02/05/2026 08:58:08</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="12" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="inlineStr"/>
+      <c r="L7" s="24" t="n">
+        <v>55</v>
+      </c>
+      <c r="M7" s="23" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="1" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="1" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="1" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>¿QUIÉN ES?</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr"/>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>¿QUÉ HIZO EL BANCO?</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr"/>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>¿CÓMO SE RESOLVIÓ?</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr"/>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>¿CUÁNDO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>USER_ID</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>NOMBRE</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>ORIGEN</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>DESTINO</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>MONTO</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>MENSAJE</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>WILLIAM TRU*</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>MZ</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>LOTE</t>
+        </is>
+      </c>
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>DIFF</t>
+        </is>
+      </c>
+      <c r="O2" s="9" t="inlineStr">
+        <is>
+          <t>MOTIVO</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>CICLO</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>FECHA_CORRECCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>U0419</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>CHARLE RIOS FLORES POLO</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Charli Flo*</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr"/>
+      <c r="G3" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>m.z L.16</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 17:48:33</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr"/>
+      <c r="N3" s="25" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O3" s="16" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>U0019</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>LIRIA PARIAMACHI DE PAZ</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Adelina Chi*</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr"/>
+      <c r="G4" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>pago de dos meses de agua y convenio.liria pariamachi</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 16:28:34</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>14/05/2026 19:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>WILLIAM TRU*</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>11A</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>14/05/2026 19:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WILLIAM TRU*</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>14/05/2026 19:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PAUL TRU*</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr"/>
+      <c r="N4" s="25" t="n">
+        <v>-30</v>
+      </c>
+      <c r="O4" s="16" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>U0169</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>DARIO DIEGO ROSALES ROMERO</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Joshelyn Rod*</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr"/>
+      <c r="G5" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>02/05/2026 08:34:41</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr"/>
+      <c r="N5" s="25" t="n">
+        <v>-42</v>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>Se corrige deuda a 17 diff 1</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>U0206</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>SAMUEL LLAMA LUNA</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Samuel Lla*</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr"/>
+      <c r="G6" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>28/04/2026 18:07:07</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>14/05/2026 19:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PAUL TRU*</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>55</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>14/05/2026 19:16</t>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M6" s="16" t="inlineStr"/>
+      <c r="N6" s="25" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O6" s="16" t="inlineStr">
+        <is>
+          <t>Se corrige deuda a 15 diff 0</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>U0172</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>OTILIA RAMIRES LUCIANO</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>TE PAGÓ</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Keimy Vel*</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>14/04/2026 19:01:18</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr"/>
+      <c r="N7" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="16" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" s="18" t="inlineStr">
+        <is>
+          <t>24/05/2026 16:44</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="K1:O1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>